--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125915121</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125915090</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125912608</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125914012</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125915416</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125914740</v>
       </c>
       <c r="B7" t="n">
-        <v>58325</v>
+        <v>58326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125915037</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125912401</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125915484</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>125915638</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>125912529</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,6 +1851,914 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126012502</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>506206</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6846806</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126012585</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>506129</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6846826</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126011409</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>506554</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6846964</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126012401</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>506229</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6846813</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126011526</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>506519</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6846862</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126012548</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>506182</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6846811</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126012549</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ryggskog, Ryggskog, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>506154</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6846771</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126012405</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56834</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ryggskog, Ryggskog, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>506277</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6846802</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126011492</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>506534</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6846929</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -2262,7 +2262,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126011526</v>
+        <v>126012548</v>
       </c>
       <c r="B18" t="n">
         <v>78968</v>
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506519</v>
+        <v>506182</v>
       </c>
       <c r="R18" t="n">
-        <v>6846862</v>
+        <v>6846811</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2330,9 +2330,19 @@
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2347,19 +2357,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126012548</v>
+        <v>126011526</v>
       </c>
       <c r="B19" t="n">
         <v>78968</v>
@@ -2394,13 +2404,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506182</v>
+        <v>506519</v>
       </c>
       <c r="R19" t="n">
-        <v>6846811</v>
+        <v>6846862</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2427,19 +2437,9 @@
           <t>2025-06-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2454,12 +2454,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126012405</v>
+        <v>126011492</v>
       </c>
       <c r="B21" t="n">
-        <v>56834</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2574,37 +2574,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506277</v>
+        <v>506534</v>
       </c>
       <c r="R21" t="n">
-        <v>6846802</v>
+        <v>6846929</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2634,11 +2634,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2653,22 +2648,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126011492</v>
+        <v>126012405</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>56834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2676,37 +2671,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506534</v>
+        <v>506277</v>
       </c>
       <c r="R22" t="n">
-        <v>6846929</v>
+        <v>6846802</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2736,6 +2731,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2750,12 +2750,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -2563,10 +2563,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126011492</v>
+        <v>126012405</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>56834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2574,37 +2574,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506534</v>
+        <v>506277</v>
       </c>
       <c r="R21" t="n">
-        <v>6846929</v>
+        <v>6846802</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2634,6 +2634,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,22 +2653,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126012405</v>
+        <v>126011492</v>
       </c>
       <c r="B22" t="n">
-        <v>56834</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2671,37 +2676,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506277</v>
+        <v>506534</v>
       </c>
       <c r="R22" t="n">
-        <v>6846802</v>
+        <v>6846929</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2731,11 +2736,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2750,12 +2750,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125915121</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125915090</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125912608</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125914012</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125915416</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125915037</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125912401</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125915484</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125915638</v>
+        <v>125912529</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506166</v>
+        <v>506229</v>
       </c>
       <c r="R12" t="n">
-        <v>6846775</v>
+        <v>6846850</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125912529</v>
+        <v>125915638</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506229</v>
+        <v>506166</v>
       </c>
       <c r="R13" t="n">
-        <v>6846850</v>
+        <v>6846775</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>126012502</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>126012585</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>126011409</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>126012401</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>126012548</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>126011526</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>126012549</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126012405</v>
+        <v>126011492</v>
       </c>
       <c r="B21" t="n">
-        <v>56834</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2574,37 +2574,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506277</v>
+        <v>506534</v>
       </c>
       <c r="R21" t="n">
-        <v>6846802</v>
+        <v>6846929</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2634,11 +2634,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2653,22 +2648,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126011492</v>
+        <v>126012405</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>56834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2676,37 +2671,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506534</v>
+        <v>506277</v>
       </c>
       <c r="R22" t="n">
-        <v>6846929</v>
+        <v>6846802</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2736,6 +2731,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2750,12 +2750,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -1660,7 +1660,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125912529</v>
+        <v>125915638</v>
       </c>
       <c r="B12" t="n">
         <v>78972</v>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506229</v>
+        <v>506166</v>
       </c>
       <c r="R12" t="n">
-        <v>6846850</v>
+        <v>6846775</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125915638</v>
+        <v>125912529</v>
       </c>
       <c r="B13" t="n">
         <v>78972</v>
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506166</v>
+        <v>506229</v>
       </c>
       <c r="R13" t="n">
-        <v>6846775</v>
+        <v>6846850</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125915121</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125915090</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125912608</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125914012</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125915416</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125914740</v>
       </c>
       <c r="B7" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125915037</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125912401</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125914813</v>
       </c>
       <c r="B10" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125915484</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>125915638</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>125912529</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>126012502</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>126012585</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>126011409</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>126012401</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>126012548</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>126011526</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>126012549</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>126011492</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>126012405</v>
       </c>
       <c r="B22" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -2563,10 +2563,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126011492</v>
+        <v>126012405</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>56835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2574,37 +2574,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506534</v>
+        <v>506277</v>
       </c>
       <c r="R21" t="n">
-        <v>6846929</v>
+        <v>6846802</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2634,6 +2634,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,22 +2653,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126012405</v>
+        <v>126011492</v>
       </c>
       <c r="B22" t="n">
-        <v>56835</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2671,37 +2676,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506277</v>
+        <v>506534</v>
       </c>
       <c r="R22" t="n">
-        <v>6846802</v>
+        <v>6846929</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2731,11 +2736,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2750,12 +2750,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -2563,10 +2563,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126012405</v>
+        <v>126011492</v>
       </c>
       <c r="B21" t="n">
-        <v>56835</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2574,37 +2574,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506277</v>
+        <v>506534</v>
       </c>
       <c r="R21" t="n">
-        <v>6846802</v>
+        <v>6846929</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2634,11 +2634,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2653,22 +2648,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126011492</v>
+        <v>126012405</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>56835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2676,37 +2671,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506534</v>
+        <v>506277</v>
       </c>
       <c r="R22" t="n">
-        <v>6846929</v>
+        <v>6846802</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2736,6 +2731,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2750,12 +2750,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -1660,7 +1660,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125915638</v>
+        <v>125912529</v>
       </c>
       <c r="B12" t="n">
         <v>78973</v>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506166</v>
+        <v>506229</v>
       </c>
       <c r="R12" t="n">
-        <v>6846775</v>
+        <v>6846850</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125912529</v>
+        <v>125915638</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506229</v>
+        <v>506166</v>
       </c>
       <c r="R13" t="n">
-        <v>6846850</v>
+        <v>6846775</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125915121</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125915090</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125912608</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125914012</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125915416</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125914740</v>
       </c>
       <c r="B7" t="n">
-        <v>58327</v>
+        <v>58331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125915037</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125912401</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125914813</v>
       </c>
       <c r="B10" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125915484</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125912529</v>
+        <v>125915638</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506229</v>
+        <v>506166</v>
       </c>
       <c r="R12" t="n">
-        <v>6846850</v>
+        <v>6846775</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125915638</v>
+        <v>125912529</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506166</v>
+        <v>506229</v>
       </c>
       <c r="R13" t="n">
-        <v>6846775</v>
+        <v>6846850</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>126012502</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>126012585</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>126011409</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>126012401</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>126012548</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>126011526</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>126012549</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>126011492</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>126012405</v>
       </c>
       <c r="B22" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -1660,7 +1660,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125915638</v>
+        <v>125912529</v>
       </c>
       <c r="B12" t="n">
         <v>78977</v>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506166</v>
+        <v>506229</v>
       </c>
       <c r="R12" t="n">
-        <v>6846775</v>
+        <v>6846850</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125912529</v>
+        <v>125915638</v>
       </c>
       <c r="B13" t="n">
         <v>78977</v>
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506229</v>
+        <v>506166</v>
       </c>
       <c r="R13" t="n">
-        <v>6846850</v>
+        <v>6846775</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125915121</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125915090</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125912608</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125914012</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125915416</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125914740</v>
       </c>
       <c r="B7" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125915037</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125912401</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125914813</v>
       </c>
       <c r="B10" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125915484</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125912529</v>
+        <v>125915638</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506229</v>
+        <v>506166</v>
       </c>
       <c r="R12" t="n">
-        <v>6846850</v>
+        <v>6846775</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125915638</v>
+        <v>125912529</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506166</v>
+        <v>506229</v>
       </c>
       <c r="R13" t="n">
-        <v>6846775</v>
+        <v>6846850</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>126012502</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>126012585</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>126011409</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>126012401</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>126012548</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>126011526</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>126012549</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126011492</v>
+        <v>126012405</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>56840</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2574,37 +2574,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506534</v>
+        <v>506277</v>
       </c>
       <c r="R21" t="n">
-        <v>6846929</v>
+        <v>6846802</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2634,6 +2634,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,22 +2653,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126012405</v>
+        <v>126011492</v>
       </c>
       <c r="B22" t="n">
-        <v>56839</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2671,37 +2676,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506277</v>
+        <v>506534</v>
       </c>
       <c r="R22" t="n">
-        <v>6846802</v>
+        <v>6846929</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2731,11 +2736,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2750,12 +2750,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -2563,10 +2563,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126012405</v>
+        <v>126011492</v>
       </c>
       <c r="B21" t="n">
-        <v>56840</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2574,37 +2574,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506277</v>
+        <v>506534</v>
       </c>
       <c r="R21" t="n">
-        <v>6846802</v>
+        <v>6846929</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2634,11 +2634,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2653,22 +2648,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126011492</v>
+        <v>126012405</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>56840</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2676,37 +2671,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506534</v>
+        <v>506277</v>
       </c>
       <c r="R22" t="n">
-        <v>6846929</v>
+        <v>6846802</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2736,6 +2731,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2750,12 +2750,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -3160,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134165721</v>
+        <v>134171488</v>
       </c>
       <c r="B27" t="n">
-        <v>58461</v>
+        <v>79359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3171,21 +3171,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506318</v>
+        <v>506322</v>
       </c>
       <c r="R27" t="n">
-        <v>6846828</v>
+        <v>6846709</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134171488</v>
+        <v>134165721</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>58461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506322</v>
+        <v>506318</v>
       </c>
       <c r="R28" t="n">
-        <v>6846709</v>
+        <v>6846828</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -2765,7 +2765,7 @@
         <v>134167808</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>134167659</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>134168213</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134171488</v>
+        <v>134165721</v>
       </c>
       <c r="B27" t="n">
-        <v>79359</v>
+        <v>58461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3171,21 +3171,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506322</v>
+        <v>506318</v>
       </c>
       <c r="R27" t="n">
-        <v>6846709</v>
+        <v>6846828</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134165721</v>
+        <v>134171488</v>
       </c>
       <c r="B28" t="n">
-        <v>58461</v>
+        <v>79366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506318</v>
+        <v>506322</v>
       </c>
       <c r="R28" t="n">
-        <v>6846828</v>
+        <v>6846709</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125915121</v>
+        <v>125912401</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Hls</t>
+          <t>Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506497</v>
+        <v>506135</v>
       </c>
       <c r="R2" t="n">
-        <v>6846793</v>
+        <v>6846802</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125915090</v>
+        <v>125912529</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506510</v>
+        <v>506229</v>
       </c>
       <c r="R3" t="n">
-        <v>6846819</v>
+        <v>6846850</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,11 +872,11 @@
         <v>125912608</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -966,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125914012</v>
+        <v>125913958</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506575</v>
+        <v>506626</v>
       </c>
       <c r="R5" t="n">
-        <v>6847222</v>
+        <v>6847210</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125915416</v>
+        <v>125914012</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1094,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506341</v>
+        <v>506575</v>
       </c>
       <c r="R6" t="n">
-        <v>6846703</v>
+        <v>6847222</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125914740</v>
+        <v>125915037</v>
       </c>
       <c r="B7" t="n">
-        <v>58334</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506636</v>
+        <v>506535</v>
       </c>
       <c r="R7" t="n">
-        <v>6846912</v>
+        <v>6846850</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125915037</v>
+        <v>125915090</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506535</v>
+        <v>506510</v>
       </c>
       <c r="R8" t="n">
-        <v>6846850</v>
+        <v>6846819</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1354,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125912401</v>
+        <v>125915121</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1385,14 +1385,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ryggskog, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506135</v>
+        <v>506497</v>
       </c>
       <c r="R9" t="n">
-        <v>6846802</v>
+        <v>6846793</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1451,55 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125914813</v>
+        <v>125915416</v>
       </c>
       <c r="B10" t="n">
-        <v>56849</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506587</v>
+        <v>506341</v>
       </c>
       <c r="R10" t="n">
-        <v>6846804</v>
+        <v>6846703</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1532,11 +1522,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Sittande i trädtopp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,11 +1551,11 @@
         <v>125915484</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1663,11 +1648,11 @@
         <v>125915638</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1757,14 +1742,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125912529</v>
+        <v>126011409</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1788,17 +1773,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506229</v>
+        <v>506554</v>
       </c>
       <c r="R13" t="n">
-        <v>6846850</v>
+        <v>6846964</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1822,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1842,26 +1827,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126012502</v>
+        <v>126011492</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1889,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506206</v>
+        <v>506534</v>
       </c>
       <c r="R14" t="n">
-        <v>6846806</v>
+        <v>6846929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,14 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126012585</v>
+        <v>126011526</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1986,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506129</v>
+        <v>506519</v>
       </c>
       <c r="R15" t="n">
-        <v>6846826</v>
+        <v>6846862</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2019,19 +2004,9 @@
           <t>2025-06-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2046,26 +2021,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126011409</v>
+        <v>126012401</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2089,17 +2064,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506554</v>
+        <v>506229</v>
       </c>
       <c r="R16" t="n">
-        <v>6846964</v>
+        <v>6846813</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2126,9 +2101,19 @@
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2143,26 +2128,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126012401</v>
+        <v>126012502</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2186,17 +2171,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506229</v>
+        <v>506206</v>
       </c>
       <c r="R17" t="n">
-        <v>6846813</v>
+        <v>6846806</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2223,19 +2208,9 @@
           <t>2025-06-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2250,12 +2225,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2265,11 +2240,11 @@
         <v>126012548</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2369,14 +2344,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126011526</v>
+        <v>126012549</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2400,14 +2375,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506519</v>
+        <v>506154</v>
       </c>
       <c r="R19" t="n">
-        <v>6846862</v>
+        <v>6846771</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2466,14 +2441,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126012549</v>
+        <v>126012585</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2497,17 +2472,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506154</v>
+        <v>506129</v>
       </c>
       <c r="R20" t="n">
-        <v>6846771</v>
+        <v>6846826</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2534,9 +2509,19 @@
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2551,26 +2536,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126011492</v>
+        <v>134167552</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2594,14 +2579,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oxmyran, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506534</v>
+        <v>506578</v>
       </c>
       <c r="R21" t="n">
-        <v>6846929</v>
+        <v>6847182</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,12 +2613,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,60 +2633,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126012405</v>
+        <v>134167659</v>
       </c>
       <c r="B22" t="n">
-        <v>56840</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506277</v>
+        <v>506574</v>
       </c>
       <c r="R22" t="n">
-        <v>6846802</v>
+        <v>6847208</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2725,17 +2710,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2765,11 +2745,11 @@
         <v>134167808</v>
       </c>
       <c r="B23" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2859,14 +2839,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134167659</v>
+        <v>134168187</v>
       </c>
       <c r="B24" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2894,13 +2874,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506574</v>
+        <v>506595</v>
       </c>
       <c r="R24" t="n">
-        <v>6847208</v>
+        <v>6847207</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2956,53 +2936,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134168231</v>
+        <v>134168213</v>
       </c>
       <c r="B25" t="n">
-        <v>57162</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506601</v>
+        <v>506598</v>
       </c>
       <c r="R25" t="n">
-        <v>6847213</v>
+        <v>6847212</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3032,6 +3007,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3058,14 +3038,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134168213</v>
+        <v>134171488</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3089,14 +3069,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Hls</t>
+          <t>Ryggskog, Ryggskog, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506598</v>
+        <v>506322</v>
       </c>
       <c r="R26" t="n">
-        <v>6847212</v>
+        <v>6846709</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3129,11 +3109,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3160,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134165721</v>
+        <v>126012229</v>
       </c>
       <c r="B27" t="n">
-        <v>58461</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3171,37 +3146,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103018</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506318</v>
+        <v>506349</v>
       </c>
       <c r="R27" t="n">
-        <v>6846828</v>
+        <v>6846844</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3225,12 +3200,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3245,22 +3220,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134171488</v>
+        <v>125913501</v>
       </c>
       <c r="B28" t="n">
-        <v>79366</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,34 +3243,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ryggskog, Ryggskog, Hls</t>
+          <t>Oxmyran, Oxmyran, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506322</v>
+        <v>506608</v>
       </c>
       <c r="R28" t="n">
-        <v>6846709</v>
+        <v>6847090</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,12 +3297,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt. Växer på Björk.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3351,6 +3331,710 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125914813</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>506587</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6846804</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Sittande i trädtopp.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134168231</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>506601</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6847213</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126012405</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ryggskog, Ryggskog, Hls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>506277</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6846802</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126091316</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>506697</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6846976</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134165721</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ryggskog, Ryggskog, Hls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>506318</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6846828</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126091302</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>506699</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6846972</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125914740</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Oxmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>506636</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6846912</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28857-2025 artfynd.xlsx
+++ b/artfynd/A 28857-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125912401</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125912529</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125912608</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125914012</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125915037</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125915090</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125915121</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125915416</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125915484</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125915638</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126011409</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126011492</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126011526</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012401</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012502</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012548</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012549</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2448,6 +2538,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012585</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2545,6 +2640,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134167552</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2642,6 +2742,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134167659</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2739,6 +2844,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134167808</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2836,6 +2946,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171488</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2933,6 +3048,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012229</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3045,6 +3165,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125914813</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3147,6 +3272,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126012405</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3244,6 +3374,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165721</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3341,6 +3476,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125913958</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3438,6 +3578,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134168187</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3540,6 +3685,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134168213</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3642,6 +3792,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125913501</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3744,6 +3899,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134168231</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3841,6 +4001,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091316</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3938,6 +4103,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091302</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4035,8 +4205,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125914740</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>